--- a/risk/Matriz de Riesgos - Tarea 2.xlsx
+++ b/risk/Matriz de Riesgos - Tarea 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffr\Dropbox\Universidad\100. Maestría\013. Seguridad en Aplicaciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffr\Desktop\aurora-threat-model\risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{9288C371-7024-4376-8F68-90360330D80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{055BBD5A-C5CA-49CD-A769-B45C806E020F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{055BBD5A-C5CA-49CD-A769-B45C806E020F}"/>
   </bookViews>
   <sheets>
     <sheet name="Parámetros" sheetId="1" r:id="rId1"/>
@@ -681,7 +681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -692,52 +692,46 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -756,7 +750,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="16">
     <dxf>
       <font>
         <b/>
@@ -806,162 +800,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4B183"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4B183"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1133,28 +971,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{17EFA96F-E0FB-4AE5-91D7-9E99C969EAB7}" name="Tabla1" displayName="Tabla1" ref="A2:B6" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{17EFA96F-E0FB-4AE5-91D7-9E99C969EAB7}" name="Tabla1" displayName="Tabla1" ref="A2:B6" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A2:B6" xr:uid="{17EFA96F-E0FB-4AE5-91D7-9E99C969EAB7}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FBE8F3BB-921A-4B86-8118-7A4A995E8AE7}" name="Impacto" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{9F8843C3-3087-48EA-8409-3117550BE29D}" name="Valor" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{FBE8F3BB-921A-4B86-8118-7A4A995E8AE7}" name="Impacto" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{9F8843C3-3087-48EA-8409-3117550BE29D}" name="Valor" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AD1593-C959-4114-AED7-E1E378A8F0AC}" name="Tabla2" displayName="Tabla2" ref="D2:E6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AD1593-C959-4114-AED7-E1E378A8F0AC}" name="Tabla2" displayName="Tabla2" ref="D2:E6" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="D2:E6" xr:uid="{87AD1593-C959-4114-AED7-E1E378A8F0AC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25596B6A-79CA-4174-863C-983FA90D56F3}" name="Probabilidad" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{B6131455-6222-4E3A-9E66-6D67CE075EDC}" name="Valor" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{25596B6A-79CA-4174-863C-983FA90D56F3}" name="Probabilidad" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{B6131455-6222-4E3A-9E66-6D67CE075EDC}" name="Valor" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1615,19 +1453,19 @@
       <c r="A12" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="15">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A12,Riesgos!$G$2:$G$26,B$11)</f>
         <v>2</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="16">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A12,Riesgos!$G$2:$G$26,C$11)</f>
         <v>5</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="17">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A12,Riesgos!$G$2:$G$26,D$11)</f>
         <v>2</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="17">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A12,Riesgos!$G$2:$G$26,E$11)</f>
         <v>1</v>
       </c>
@@ -1640,19 +1478,19 @@
       <c r="A13" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="15">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A13,Riesgos!$G$2:$G$26,B$11)</f>
         <v>1</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="16">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A13,Riesgos!$G$2:$G$26,C$11)</f>
         <v>4</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="17">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A13,Riesgos!$G$2:$G$26,D$11)</f>
         <v>2</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="17">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A13,Riesgos!$G$2:$G$26,E$11)</f>
         <v>0</v>
       </c>
@@ -1665,19 +1503,19 @@
       <c r="A14" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="14">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A14,Riesgos!$G$2:$G$26,B$11)</f>
         <v>1</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="15">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A14,Riesgos!$G$2:$G$26,C$11)</f>
         <v>3</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="16">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A14,Riesgos!$G$2:$G$26,D$11)</f>
         <v>1</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="16">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A14,Riesgos!$G$2:$G$26,E$11)</f>
         <v>0</v>
       </c>
@@ -1690,19 +1528,19 @@
       <c r="A15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="14">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A15,Riesgos!$G$2:$G$26,B$11)</f>
         <v>1</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="14">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A15,Riesgos!$G$2:$G$26,C$11)</f>
         <v>1</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="15">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A15,Riesgos!$G$2:$G$26,D$11)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="15">
         <f>COUNTIFS(Riesgos!$F$2:$F$26,$A15,Riesgos!$G$2:$G$26,E$11)</f>
         <v>0</v>
       </c>
@@ -1712,26 +1550,26 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <f>SUM(B12:B15)</f>
         <v>5</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="9">
         <f t="shared" ref="C16:E16" si="1">SUM(C12:C15)</f>
         <v>13</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="9">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <f>SUM(B12:E15)</f>
         <v>25</v>
       </c>
@@ -1745,7 +1583,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B20" s="5">
@@ -1754,7 +1592,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="5">
@@ -1763,7 +1601,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="12" t="s">
         <v>5</v>
       </c>
       <c r="B22" s="5">
@@ -1772,7 +1610,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="13" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="7">
@@ -1819,43 +1657,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1895,7 +1733,7 @@
       <c r="K2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="20">
+      <c r="L2" s="18">
         <v>46394</v>
       </c>
       <c r="M2" s="9" t="s">
@@ -1938,7 +1776,7 @@
       <c r="K3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="18">
         <v>46484</v>
       </c>
       <c r="M3" s="9" t="s">
@@ -1981,7 +1819,7 @@
       <c r="K4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="20">
+      <c r="L4" s="18">
         <v>46394</v>
       </c>
       <c r="M4" s="9" t="s">
@@ -2024,7 +1862,7 @@
       <c r="K5" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="L5" s="20">
+      <c r="L5" s="18">
         <v>46394</v>
       </c>
       <c r="M5" s="9" t="s">
@@ -2067,7 +1905,7 @@
       <c r="K6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="18">
         <v>46484</v>
       </c>
       <c r="M6" s="9" t="s">
@@ -2110,7 +1948,7 @@
       <c r="K7" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L7" s="20">
+      <c r="L7" s="18">
         <v>46484</v>
       </c>
       <c r="M7" s="9" t="s">
@@ -2153,7 +1991,7 @@
       <c r="K8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="L8" s="20">
+      <c r="L8" s="18">
         <v>46484</v>
       </c>
       <c r="M8" s="9" t="s">
@@ -2196,7 +2034,7 @@
       <c r="K9" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="18">
         <v>46484</v>
       </c>
       <c r="M9" s="9" t="s">
@@ -2239,7 +2077,7 @@
       <c r="K10" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="18">
         <v>46667</v>
       </c>
       <c r="M10" s="9" t="s">
@@ -2282,7 +2120,7 @@
       <c r="K11" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="18">
         <v>46394</v>
       </c>
       <c r="M11" s="9" t="s">
@@ -2325,7 +2163,7 @@
       <c r="K12" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L12" s="20">
+      <c r="L12" s="18">
         <v>46484</v>
       </c>
       <c r="M12" s="9" t="s">
@@ -2368,7 +2206,7 @@
       <c r="K13" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="L13" s="20">
+      <c r="L13" s="18">
         <v>46394</v>
       </c>
       <c r="M13" s="9" t="s">
@@ -2411,7 +2249,7 @@
       <c r="K14" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="L14" s="20">
+      <c r="L14" s="18">
         <v>46394</v>
       </c>
       <c r="M14" s="9" t="s">
@@ -2454,7 +2292,7 @@
       <c r="K15" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="L15" s="20">
+      <c r="L15" s="18">
         <v>46484</v>
       </c>
       <c r="M15" s="9" t="s">
@@ -2497,7 +2335,7 @@
       <c r="K16" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="L16" s="20">
+      <c r="L16" s="18">
         <v>46394</v>
       </c>
       <c r="M16" s="9" t="s">
@@ -2540,7 +2378,7 @@
       <c r="K17" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="L17" s="20">
+      <c r="L17" s="18">
         <v>46667</v>
       </c>
       <c r="M17" s="9" t="s">
@@ -2583,7 +2421,7 @@
       <c r="K18" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="L18" s="20">
+      <c r="L18" s="18">
         <v>46667</v>
       </c>
       <c r="M18" s="9" t="s">
@@ -2626,7 +2464,7 @@
       <c r="K19" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="L19" s="20">
+      <c r="L19" s="18">
         <v>46484</v>
       </c>
       <c r="M19" s="9" t="s">
@@ -2669,7 +2507,7 @@
       <c r="K20" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="L20" s="20">
+      <c r="L20" s="18">
         <v>46484</v>
       </c>
       <c r="M20" s="9" t="s">
@@ -2712,7 +2550,7 @@
       <c r="K21" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="L21" s="20">
+      <c r="L21" s="18">
         <v>46484</v>
       </c>
       <c r="M21" s="9" t="s">
@@ -2755,7 +2593,7 @@
       <c r="K22" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="L22" s="20">
+      <c r="L22" s="18">
         <v>46484</v>
       </c>
       <c r="M22" s="9" t="s">
@@ -2798,7 +2636,7 @@
       <c r="K23" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="L23" s="20">
+      <c r="L23" s="18">
         <v>46394</v>
       </c>
       <c r="M23" s="9" t="s">
@@ -2841,7 +2679,7 @@
       <c r="K24" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="L24" s="20">
+      <c r="L24" s="18">
         <v>46667</v>
       </c>
       <c r="M24" s="9" t="s">
@@ -2884,7 +2722,7 @@
       <c r="K25" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="L25" s="22">
+      <c r="L25" s="20">
         <v>46667</v>
       </c>
       <c r="M25" s="9" t="s">
@@ -2927,7 +2765,7 @@
       <c r="K26" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="L26" s="23">
+      <c r="L26" s="21">
         <v>46667</v>
       </c>
       <c r="M26" s="9" t="s">
@@ -2936,16 +2774,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I26">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"Crítico"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"Alto"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Medio"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Bajo"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2974,43 +2812,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3050,7 +2888,7 @@
       <c r="K2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="20">
+      <c r="L2" s="18">
         <v>46394</v>
       </c>
       <c r="M2" s="9" t="s">
@@ -3093,7 +2931,7 @@
       <c r="K3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="18">
         <v>46484</v>
       </c>
       <c r="M3" s="9" t="s">
@@ -3136,7 +2974,7 @@
       <c r="K4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="20">
+      <c r="L4" s="18">
         <v>46394</v>
       </c>
       <c r="M4" s="9" t="s">
@@ -3179,7 +3017,7 @@
       <c r="K5" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="L5" s="20">
+      <c r="L5" s="18">
         <v>46394</v>
       </c>
       <c r="M5" s="9" t="s">
@@ -3222,7 +3060,7 @@
       <c r="K6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="18">
         <v>46484</v>
       </c>
       <c r="M6" s="9" t="s">
@@ -3265,7 +3103,7 @@
       <c r="K7" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L7" s="20">
+      <c r="L7" s="18">
         <v>46484</v>
       </c>
       <c r="M7" s="9" t="s">
@@ -3308,7 +3146,7 @@
       <c r="K8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="L8" s="20">
+      <c r="L8" s="18">
         <v>46484</v>
       </c>
       <c r="M8" s="9" t="s">
@@ -3351,7 +3189,7 @@
       <c r="K9" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="18">
         <v>46484</v>
       </c>
       <c r="M9" s="9" t="s">
@@ -3394,7 +3232,7 @@
       <c r="K10" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="18">
         <v>46667</v>
       </c>
       <c r="M10" s="9" t="s">
@@ -3437,7 +3275,7 @@
       <c r="K11" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="18">
         <v>46394</v>
       </c>
       <c r="M11" s="9" t="s">
